--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/ALABAMA_2014.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/ALABAMA_2014.xlsx
@@ -2004,7 +2004,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C92">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C134">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C221">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C229">
@@ -10212,7 +10212,7 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C548">
@@ -11238,7 +11238,7 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C605">
@@ -11616,7 +11616,7 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C626">
@@ -17970,7 +17970,7 @@
       </c>
       <c r="B979" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C979">
